--- a/Immunity/Tolerance.v.Resistance/Howick_2017/Howick_SNPs.xlsx
+++ b/Immunity/Tolerance.v.Resistance/Howick_2017/Howick_SNPs.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\thesis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://adcsuf-my.sharepoint.com/personal/tconyers_csu_fullerton_edu/Documents/Documents/GitHub/Thesis_Project/Immunity/Tolerance.v.Resistance/Howick_2017/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47B885E6-3241-4A1F-A9E3-646E238A6E14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{47B885E6-3241-4A1F-A9E3-646E238A6E14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BD5EDEF7-F7FA-4DB1-B66C-A396B4528B07}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1597,6 +1597,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DB00FBF-3C43-4495-A565-A3CA0465ABBA}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:G59"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1631,7 +1632,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="42" t="s">
         <v>111</v>
       </c>
@@ -1654,7 +1655,7 @@
         <v>4.9399999999999997E-4</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="42" t="s">
         <v>111</v>
       </c>
@@ -1677,7 +1678,7 @@
         <v>1.14E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="42" t="s">
         <v>111</v>
       </c>
@@ -1700,7 +1701,7 @@
         <v>1.21E-4</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="42" t="s">
         <v>111</v>
       </c>
@@ -1723,7 +1724,7 @@
         <v>1.33E-3</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="42" t="s">
         <v>111</v>
       </c>
@@ -1746,7 +1747,7 @@
         <v>2.3499999999999999E-4</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="42" t="s">
         <v>111</v>
       </c>
@@ -1769,7 +1770,7 @@
         <v>1.49E-5</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="42" t="s">
         <v>111</v>
       </c>
@@ -1792,7 +1793,7 @@
         <v>3.59E-4</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="42" t="s">
         <v>111</v>
       </c>
@@ -1815,7 +1816,7 @@
         <v>1.01E-5</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="42" t="s">
         <v>111</v>
       </c>
@@ -1838,7 +1839,7 @@
         <v>6.8999999999999997E-5</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="42" t="s">
         <v>111</v>
       </c>
@@ -1861,7 +1862,7 @@
         <v>8.25E-5</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="42" t="s">
         <v>111</v>
       </c>
@@ -1884,7 +1885,7 @@
         <v>9.4300000000000002E-5</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="42" t="s">
         <v>111</v>
       </c>
@@ -1907,7 +1908,7 @@
         <v>1.6899999999999999E-4</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="42" t="s">
         <v>111</v>
       </c>
@@ -1930,7 +1931,7 @@
         <v>2.4499999999999999E-5</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="42" t="s">
         <v>111</v>
       </c>
@@ -1953,7 +1954,7 @@
         <v>2.4399999999999999E-4</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="42" t="s">
         <v>111</v>
       </c>
@@ -1976,7 +1977,7 @@
         <v>3.4699999999999998E-6</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="42" t="s">
         <v>111</v>
       </c>
@@ -1999,7 +2000,7 @@
         <v>2.8800000000000002E-3</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="42" t="s">
         <v>111</v>
       </c>
@@ -2022,7 +2023,7 @@
         <v>4.9599999999999999E-6</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="42" t="s">
         <v>111</v>
       </c>
@@ -2045,7 +2046,7 @@
         <v>1.12E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="42" t="s">
         <v>111</v>
       </c>
@@ -2068,7 +2069,7 @@
         <v>1.15E-3</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="42" t="s">
         <v>111</v>
       </c>
@@ -2091,7 +2092,7 @@
         <v>8.9800000000000004E-4</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="42" t="s">
         <v>111</v>
       </c>
@@ -2114,7 +2115,7 @@
         <v>1.7000000000000001E-4</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="42" t="s">
         <v>111</v>
       </c>
@@ -2137,7 +2138,7 @@
         <v>8.9499999999999996E-4</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="42" t="s">
         <v>111</v>
       </c>
@@ -2160,7 +2161,7 @@
         <v>8.9499999999999996E-4</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="42" t="s">
         <v>111</v>
       </c>
@@ -2183,7 +2184,7 @@
         <v>8.5699999999999995E-3</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="42" t="s">
         <v>111</v>
       </c>
@@ -2206,7 +2207,7 @@
         <v>1.8699999999999999E-3</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="42" t="s">
         <v>111</v>
       </c>
@@ -2229,7 +2230,7 @@
         <v>8.9299999999999992E-6</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="42" t="s">
         <v>111</v>
       </c>
@@ -2252,7 +2253,7 @@
         <v>3.6000000000000002E-4</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="42" t="s">
         <v>111</v>
       </c>
@@ -2275,7 +2276,7 @@
         <v>5.3600000000000002E-4</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="42" t="s">
         <v>111</v>
       </c>
@@ -2966,7 +2967,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G59" xr:uid="{6DB00FBF-3C43-4495-A565-A3CA0465ABBA}"/>
+  <autoFilter ref="A1:G59" xr:uid="{6DB00FBF-3C43-4495-A565-A3CA0465ABBA}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="Resistance"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <hyperlinks>
     <hyperlink ref="B31" r:id="rId1" display="http://flybase.org/cgi-bin/gbrowse2/dmel/?ref=X%3Bstart%3D20133406%3Bstop%3D20133406" xr:uid="{B8FC0999-7616-49F1-87A3-1B3E3F59521B}"/>
     <hyperlink ref="B32" r:id="rId2" display="http://flybase.org/cgi-bin/gbrowse2/dmel/?ref=X%3Bstart%3D20133406%3Bstop%3D20133406" xr:uid="{D12D4682-7263-4AE7-87E3-952622B7910D}"/>

--- a/Immunity/Tolerance.v.Resistance/Howick_2017/Howick_SNPs.xlsx
+++ b/Immunity/Tolerance.v.Resistance/Howick_2017/Howick_SNPs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://adcsuf-my.sharepoint.com/personal/tconyers_csu_fullerton_edu/Documents/Documents/GitHub/Thesis_Project/Immunity/Tolerance.v.Resistance/Howick_2017/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{47B885E6-3241-4A1F-A9E3-646E238A6E14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BD5EDEF7-F7FA-4DB1-B66C-A396B4528B07}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="13_ncr:1_{47B885E6-3241-4A1F-A9E3-646E238A6E14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{871AE8A1-847E-47EB-87E1-48C5B864ED3A}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,16 +42,6 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>X:20,133,406</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
       <t>CG15322</t>
     </r>
   </si>
@@ -82,16 +72,6 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>2R:20,102,058</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
       <t>none annotated</t>
     </r>
   </si>
@@ -112,27 +92,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>X:20,032,422</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
       <t>D2R</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>2R:22,444,306</t>
     </r>
   </si>
   <si>
@@ -161,16 +121,6 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>3L:1,909,764</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
       <t>CG1887</t>
     </r>
   </si>
@@ -191,16 +141,6 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>2R:21,681,039</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
       <t>CG30263</t>
     </r>
   </si>
@@ -221,16 +161,6 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>X:5,760,226</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
       <t>MAPk-Ak2</t>
     </r>
   </si>
@@ -251,26 +181,6 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>3L:1,108,730</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>2L:382,411</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
       <t>al</t>
     </r>
   </si>
@@ -281,46 +191,6 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>X:18,923,524</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>X:18,923,637</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>2R:20,102,018</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>X:20,854,194</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
       <t>shakB</t>
     </r>
   </si>
@@ -331,16 +201,6 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>2L:9,926,696</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
       <t>CG42366</t>
     </r>
   </si>
@@ -351,16 +211,6 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>2R:20,289,946</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
       <t>CkIIbeta2</t>
     </r>
   </si>
@@ -371,26 +221,6 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>2R:20,289,993</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>3R:30,255,259</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
       <t>CG18404</t>
     </r>
   </si>
@@ -421,16 +251,6 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>X:6,206,890</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
       <t>vanin-like</t>
     </r>
   </si>
@@ -441,26 +261,6 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>X:20,707,400</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>2L:10,686,264</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
       <t>CG7296</t>
     </r>
   </si>
@@ -481,37 +281,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>2L:383,384</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>2R:18,866,081</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
       <t>Dpt</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>X:9,230,968</t>
     </r>
   </si>
   <si>
@@ -550,16 +320,6 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>3L:8,732,726</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
       <t>Cp16</t>
     </r>
   </si>
@@ -571,16 +331,6 @@
         <family val="2"/>
       </rPr>
       <t>Prm</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>3L:15,942,843</t>
     </r>
   </si>
   <si>
@@ -1043,6 +793,81 @@
       </rPr>
       <t>value</t>
     </r>
+  </si>
+  <si>
+    <t>X:20,133,406</t>
+  </si>
+  <si>
+    <t>2R:20,102,058</t>
+  </si>
+  <si>
+    <t>X:20,032,422</t>
+  </si>
+  <si>
+    <t>2R:22,444,306</t>
+  </si>
+  <si>
+    <t>3L:1,909,764</t>
+  </si>
+  <si>
+    <t>2R:21,681,039</t>
+  </si>
+  <si>
+    <t>X:5,760,226</t>
+  </si>
+  <si>
+    <t>3L:1,108,730</t>
+  </si>
+  <si>
+    <t>2L:382,411</t>
+  </si>
+  <si>
+    <t>X:18,923,524</t>
+  </si>
+  <si>
+    <t>X:18,923,637</t>
+  </si>
+  <si>
+    <t>2R:20,102,018</t>
+  </si>
+  <si>
+    <t>X:20,854,194</t>
+  </si>
+  <si>
+    <t>2L:9,926,696</t>
+  </si>
+  <si>
+    <t>2R:20,289,946</t>
+  </si>
+  <si>
+    <t>2R:20,289,993</t>
+  </si>
+  <si>
+    <t>3R:30,255,259</t>
+  </si>
+  <si>
+    <t>X:6,206,890</t>
+  </si>
+  <si>
+    <t>X:20,707,400</t>
+  </si>
+  <si>
+    <t>2L:10,686,264</t>
+  </si>
+  <si>
+    <t>2L:383,384</t>
+  </si>
+  <si>
+    <t>2R:18,866,081</t>
+  </si>
+  <si>
+    <t>X:9,230,968</t>
+  </si>
+  <si>
+    <t>3L:8,732,726</t>
+  </si>
+  <si>
+    <t>3L:15,942,843</t>
   </si>
 </sst>
 </file>
@@ -1308,6 +1133,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1597,7 +1426,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DB00FBF-3C43-4495-A565-A3CA0465ABBA}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:G59"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1611,39 +1439,39 @@
   <sheetData>
     <row r="1" spans="1:7" ht="24" x14ac:dyDescent="0.25">
       <c r="A1" s="44" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
       <c r="B1" s="44" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="44" t="s">
-        <v>114</v>
+        <v>89</v>
       </c>
       <c r="D1" s="45" t="s">
-        <v>115</v>
+        <v>90</v>
       </c>
       <c r="E1" s="44" t="s">
-        <v>116</v>
+        <v>91</v>
       </c>
       <c r="F1" s="45" t="s">
-        <v>117</v>
+        <v>92</v>
       </c>
       <c r="G1" s="43" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="42" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="B2" s="42" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="C2" s="42" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D2" s="42" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E2" s="41">
         <v>7.8100000000000002E-7</v>
@@ -1655,18 +1483,18 @@
         <v>4.9399999999999997E-4</v>
       </c>
     </row>
-    <row r="3" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="42" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="B3" s="35" t="s">
-        <v>109</v>
+        <v>84</v>
       </c>
       <c r="C3" s="35" t="s">
-        <v>108</v>
+        <v>83</v>
       </c>
       <c r="D3" s="35" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E3" s="34">
         <v>9.7199999999999997E-7</v>
@@ -1678,18 +1506,18 @@
         <v>1.14E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="42" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="B4" s="39" t="s">
-        <v>107</v>
+        <v>82</v>
       </c>
       <c r="C4" s="39" t="s">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="D4" s="39" t="s">
-        <v>106</v>
+        <v>81</v>
       </c>
       <c r="E4" s="38">
         <v>1.39E-6</v>
@@ -1701,18 +1529,18 @@
         <v>1.21E-4</v>
       </c>
     </row>
-    <row r="5" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="42" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="B5" s="35" t="s">
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="C5" s="35" t="s">
-        <v>104</v>
+        <v>79</v>
       </c>
       <c r="D5" s="35" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E5" s="34">
         <v>1.8500000000000001E-6</v>
@@ -1724,18 +1552,18 @@
         <v>1.33E-3</v>
       </c>
     </row>
-    <row r="6" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="42" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="B6" s="39" t="s">
-        <v>103</v>
+        <v>78</v>
       </c>
       <c r="C6" s="39" t="s">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="D6" s="39" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E6" s="38">
         <v>2.3800000000000001E-6</v>
@@ -1747,18 +1575,18 @@
         <v>2.3499999999999999E-4</v>
       </c>
     </row>
-    <row r="7" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="42" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="B7" s="35" t="s">
-        <v>101</v>
+        <v>76</v>
       </c>
       <c r="C7" s="35" t="s">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="D7" s="35" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E7" s="34">
         <v>2.5000000000000002E-6</v>
@@ -1770,18 +1598,18 @@
         <v>1.49E-5</v>
       </c>
     </row>
-    <row r="8" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="42" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="B8" s="39" t="s">
-        <v>99</v>
+        <v>74</v>
       </c>
       <c r="C8" s="39" t="s">
-        <v>98</v>
+        <v>73</v>
       </c>
       <c r="D8" s="39" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E8" s="38">
         <v>3.5099999999999999E-6</v>
@@ -1793,18 +1621,18 @@
         <v>3.59E-4</v>
       </c>
     </row>
-    <row r="9" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="42" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="B9" s="35" t="s">
-        <v>97</v>
+        <v>72</v>
       </c>
       <c r="C9" s="35" t="s">
-        <v>96</v>
+        <v>71</v>
       </c>
       <c r="D9" s="35" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="E9" s="34">
         <v>3.72E-6</v>
@@ -1816,18 +1644,18 @@
         <v>1.01E-5</v>
       </c>
     </row>
-    <row r="10" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="42" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="B10" s="39" t="s">
-        <v>95</v>
+        <v>70</v>
       </c>
       <c r="C10" s="39" t="s">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="D10" s="39" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E10" s="38">
         <v>4.2200000000000003E-6</v>
@@ -1839,18 +1667,18 @@
         <v>6.8999999999999997E-5</v>
       </c>
     </row>
-    <row r="11" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="42" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="B11" s="35" t="s">
-        <v>94</v>
+        <v>69</v>
       </c>
       <c r="C11" s="35" t="s">
-        <v>93</v>
+        <v>68</v>
       </c>
       <c r="D11" s="35" t="s">
-        <v>92</v>
+        <v>67</v>
       </c>
       <c r="E11" s="34">
         <v>4.8799999999999999E-6</v>
@@ -1862,18 +1690,18 @@
         <v>8.25E-5</v>
       </c>
     </row>
-    <row r="12" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="42" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="B12" s="39" t="s">
-        <v>91</v>
+        <v>66</v>
       </c>
       <c r="C12" s="39" t="s">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="D12" s="39" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E12" s="38">
         <v>4.9599999999999999E-6</v>
@@ -1885,18 +1713,18 @@
         <v>9.4300000000000002E-5</v>
       </c>
     </row>
-    <row r="13" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="42" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="B13" s="35" t="s">
-        <v>89</v>
+        <v>64</v>
       </c>
       <c r="C13" s="35" t="s">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="D13" s="35" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E13" s="34">
         <v>5.1399999999999999E-6</v>
@@ -1908,18 +1736,18 @@
         <v>1.6899999999999999E-4</v>
       </c>
     </row>
-    <row r="14" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="42" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="B14" s="39" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="C14" s="39" t="s">
-        <v>86</v>
+        <v>61</v>
       </c>
       <c r="D14" s="39" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E14" s="38">
         <v>5.3199999999999999E-6</v>
@@ -1931,18 +1759,18 @@
         <v>2.4499999999999999E-5</v>
       </c>
     </row>
-    <row r="15" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="42" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="B15" s="35" t="s">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="C15" s="35" t="s">
-        <v>84</v>
+        <v>59</v>
       </c>
       <c r="D15" s="35" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E15" s="34">
         <v>5.66E-6</v>
@@ -1954,18 +1782,18 @@
         <v>2.4399999999999999E-4</v>
       </c>
     </row>
-    <row r="16" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="42" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="B16" s="39" t="s">
-        <v>83</v>
+        <v>58</v>
       </c>
       <c r="C16" s="39" t="s">
-        <v>82</v>
+        <v>57</v>
       </c>
       <c r="D16" s="39" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="E16" s="38">
         <v>5.9000000000000003E-6</v>
@@ -1977,18 +1805,18 @@
         <v>3.4699999999999998E-6</v>
       </c>
     </row>
-    <row r="17" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="42" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="B17" s="35" t="s">
-        <v>81</v>
+        <v>56</v>
       </c>
       <c r="C17" s="35" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="D17" s="35" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="E17" s="34">
         <v>5.9100000000000002E-6</v>
@@ -2000,18 +1828,18 @@
         <v>2.8800000000000002E-3</v>
       </c>
     </row>
-    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="42" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="B18" s="39" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="C18" s="39" t="s">
-        <v>77</v>
+        <v>52</v>
       </c>
       <c r="D18" s="39" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E18" s="38">
         <v>6.1500000000000004E-6</v>
@@ -2023,18 +1851,18 @@
         <v>4.9599999999999999E-6</v>
       </c>
     </row>
-    <row r="19" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="42" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="B19" s="35" t="s">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="C19" s="35" t="s">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="D19" s="35" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E19" s="34">
         <v>6.5200000000000003E-6</v>
@@ -2046,18 +1874,18 @@
         <v>1.12E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="42" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="B20" s="39" t="s">
-        <v>74</v>
+        <v>49</v>
       </c>
       <c r="C20" s="39" t="s">
-        <v>73</v>
+        <v>48</v>
       </c>
       <c r="D20" s="39" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E20" s="38">
         <v>6.5699999999999998E-6</v>
@@ -2069,18 +1897,18 @@
         <v>1.15E-3</v>
       </c>
     </row>
-    <row r="21" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="42" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="B21" s="35" t="s">
-        <v>72</v>
+        <v>47</v>
       </c>
       <c r="C21" s="35" t="s">
-        <v>71</v>
+        <v>46</v>
       </c>
       <c r="D21" s="35" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E21" s="34">
         <v>6.5799999999999997E-6</v>
@@ -2092,18 +1920,18 @@
         <v>8.9800000000000004E-4</v>
       </c>
     </row>
-    <row r="22" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="42" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="B22" s="39" t="s">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="C22" s="39" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D22" s="39" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E22" s="38">
         <v>8.3100000000000001E-6</v>
@@ -2115,18 +1943,18 @@
         <v>1.7000000000000001E-4</v>
       </c>
     </row>
-    <row r="23" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="42" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="B23" s="35" t="s">
-        <v>68</v>
+        <v>43</v>
       </c>
       <c r="C23" s="35" t="s">
-        <v>69</v>
+        <v>44</v>
       </c>
       <c r="D23" s="35" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="E23" s="34">
         <v>8.49E-6</v>
@@ -2138,18 +1966,18 @@
         <v>8.9499999999999996E-4</v>
       </c>
     </row>
-    <row r="24" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="42" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="B24" s="39" t="s">
-        <v>68</v>
+        <v>43</v>
       </c>
       <c r="C24" s="39" t="s">
-        <v>67</v>
+        <v>42</v>
       </c>
       <c r="D24" s="39" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E24" s="38">
         <v>8.49E-6</v>
@@ -2161,18 +1989,18 @@
         <v>8.9499999999999996E-4</v>
       </c>
     </row>
-    <row r="25" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="42" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="B25" s="35" t="s">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="C25" s="35" t="s">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="D25" s="35" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E25" s="34">
         <v>8.6600000000000001E-6</v>
@@ -2184,18 +2012,18 @@
         <v>8.5699999999999995E-3</v>
       </c>
     </row>
-    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="42" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="B26" s="39" t="s">
-        <v>64</v>
+        <v>39</v>
       </c>
       <c r="C26" s="39" t="s">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="D26" s="39" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E26" s="38">
         <v>8.9800000000000004E-6</v>
@@ -2207,18 +2035,18 @@
         <v>1.8699999999999999E-3</v>
       </c>
     </row>
-    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="42" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="B27" s="35" t="s">
-        <v>62</v>
+        <v>37</v>
       </c>
       <c r="C27" s="35" t="s">
-        <v>61</v>
+        <v>36</v>
       </c>
       <c r="D27" s="35" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E27" s="34">
         <v>9.0000000000000002E-6</v>
@@ -2230,18 +2058,18 @@
         <v>8.9299999999999992E-6</v>
       </c>
     </row>
-    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="42" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="B28" s="39" t="s">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="C28" s="39" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D28" s="39" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E28" s="38">
         <v>9.1700000000000003E-6</v>
@@ -2253,18 +2081,18 @@
         <v>3.6000000000000002E-4</v>
       </c>
     </row>
-    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="42" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="B29" s="36" t="s">
-        <v>59</v>
+        <v>34</v>
       </c>
       <c r="C29" s="35" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="D29" s="35" t="s">
-        <v>57</v>
+        <v>32</v>
       </c>
       <c r="E29" s="34">
         <v>9.4399999999999994E-6</v>
@@ -2276,18 +2104,18 @@
         <v>5.3600000000000002E-4</v>
       </c>
     </row>
-    <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="42" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="B30" s="32" t="s">
-        <v>56</v>
+        <v>31</v>
       </c>
       <c r="C30" s="32" t="s">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="D30" s="32" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E30" s="31">
         <v>9.5400000000000001E-6</v>
@@ -2301,16 +2129,16 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="42" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="B31" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C31" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="D31" s="2" t="s">
         <v>2</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>3</v>
       </c>
       <c r="E31" s="4">
         <v>0.86260000000000003</v>
@@ -2324,16 +2152,16 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="42" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>1</v>
+        <v>94</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E32" s="9">
         <v>0.86260000000000003</v>
@@ -2347,16 +2175,16 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="42" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="B33" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="C33" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="D33" s="12" t="s">
         <v>5</v>
-      </c>
-      <c r="C33" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="D33" s="12" t="s">
-        <v>7</v>
       </c>
       <c r="E33" s="14">
         <v>0.11849999999999999</v>
@@ -2370,16 +2198,16 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="42" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>8</v>
+        <v>96</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E34" s="9">
         <v>0.77449999999999997</v>
@@ -2393,16 +2221,16 @@
     </row>
     <row r="35" spans="1:7" ht="22.8" x14ac:dyDescent="0.25">
       <c r="A35" s="42" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="B35" s="11" t="s">
-        <v>10</v>
+        <v>97</v>
       </c>
       <c r="C35" s="16" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E35" s="14">
         <v>0.31940000000000002</v>
@@ -2416,16 +2244,16 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="42" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>12</v>
+        <v>98</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E36" s="9">
         <v>0.86370000000000002</v>
@@ -2439,16 +2267,16 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="42" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>15</v>
+        <v>99</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D37" s="12" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E37" s="18">
         <v>0.90100000000000002</v>
@@ -2462,16 +2290,16 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="42" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>18</v>
+        <v>100</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E38" s="9">
         <v>0.79869999999999997</v>
@@ -2485,16 +2313,16 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="42" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="B39" s="20" t="s">
-        <v>21</v>
+        <v>101</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D39" s="12" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E39" s="14">
         <v>0.44019999999999998</v>
@@ -2508,16 +2336,16 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="42" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>22</v>
+        <v>102</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E40" s="9">
         <v>0.16070000000000001</v>
@@ -2531,16 +2359,16 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="42" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="B41" s="20" t="s">
-        <v>24</v>
+        <v>103</v>
       </c>
       <c r="C41" s="12" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D41" s="12" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E41" s="14">
         <v>0.8659</v>
@@ -2554,16 +2382,16 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="42" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>25</v>
+        <v>104</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E42" s="9">
         <v>0.95450000000000002</v>
@@ -2577,16 +2405,16 @@
     </row>
     <row r="43" spans="1:7" ht="22.8" x14ac:dyDescent="0.25">
       <c r="A43" s="42" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="B43" s="11" t="s">
-        <v>26</v>
+        <v>105</v>
       </c>
       <c r="C43" s="16" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D43" s="12" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E43" s="14">
         <v>0.1983</v>
@@ -2600,16 +2428,16 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="42" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>27</v>
+        <v>106</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E44" s="23">
         <v>0.746</v>
@@ -2623,16 +2451,16 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="42" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="B45" s="11" t="s">
-        <v>29</v>
+        <v>107</v>
       </c>
       <c r="C45" s="12" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="D45" s="12" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E45" s="19">
         <v>1.5839999999999999E-3</v>
@@ -2646,16 +2474,16 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="42" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>31</v>
+        <v>108</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="D46" s="7" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E46" s="15">
         <v>5.4719999999999998E-2</v>
@@ -2669,16 +2497,16 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="42" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="B47" s="11" t="s">
-        <v>33</v>
+        <v>109</v>
       </c>
       <c r="C47" s="12" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="D47" s="12" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E47" s="22">
         <v>1.155E-2</v>
@@ -2692,16 +2520,16 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="42" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>34</v>
+        <v>110</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="D48" s="7" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="E48" s="15">
         <v>4.3540000000000002E-2</v>
@@ -2715,16 +2543,16 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="42" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="B49" s="11" t="s">
-        <v>34</v>
+        <v>110</v>
       </c>
       <c r="C49" s="12" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="D49" s="12" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="E49" s="22">
         <v>4.3540000000000002E-2</v>
@@ -2738,16 +2566,16 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="42" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>38</v>
+        <v>111</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="D50" s="7" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E50" s="9">
         <v>0.89839999999999998</v>
@@ -2761,16 +2589,16 @@
     </row>
     <row r="51" spans="1:7" ht="22.8" x14ac:dyDescent="0.25">
       <c r="A51" s="42" t="s">
+        <v>87</v>
+      </c>
+      <c r="B51" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="B51" s="11" t="s">
-        <v>40</v>
-      </c>
       <c r="C51" s="16" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D51" s="12" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E51" s="14">
         <v>0.96489999999999998</v>
@@ -2784,16 +2612,16 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="42" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>41</v>
+        <v>113</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="D52" s="7" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="E52" s="9">
         <v>0.14580000000000001</v>
@@ -2807,16 +2635,16 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="42" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="B53" s="11" t="s">
-        <v>41</v>
+        <v>113</v>
       </c>
       <c r="C53" s="12" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="D53" s="12" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E53" s="14">
         <v>0.14580000000000001</v>
@@ -2830,16 +2658,16 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="42" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>44</v>
+        <v>114</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="D54" s="7" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E54" s="9">
         <v>0.78249999999999997</v>
@@ -2853,16 +2681,16 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="42" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="B55" s="11" t="s">
-        <v>45</v>
+        <v>115</v>
       </c>
       <c r="C55" s="12" t="s">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="D55" s="12" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E55" s="19">
         <v>1.05E-4</v>
@@ -2876,16 +2704,16 @@
     </row>
     <row r="56" spans="1:7" ht="22.8" x14ac:dyDescent="0.25">
       <c r="A56" s="42" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>47</v>
+        <v>116</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="D56" s="24" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="E56" s="9">
         <v>0.69179999999999997</v>
@@ -2899,16 +2727,16 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="42" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="B57" s="11" t="s">
-        <v>50</v>
+        <v>117</v>
       </c>
       <c r="C57" s="12" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="D57" s="12" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="E57" s="14">
         <v>0.98270000000000002</v>
@@ -2922,16 +2750,16 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="42" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>50</v>
+        <v>117</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="D58" s="7" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="E58" s="9">
         <v>0.98270000000000002</v>
@@ -2945,16 +2773,16 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="42" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="B59" s="25" t="s">
-        <v>53</v>
+        <v>118</v>
       </c>
       <c r="C59" s="26" t="s">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="D59" s="26" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E59" s="28">
         <v>0.3589</v>
@@ -2967,44 +2795,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G59" xr:uid="{6DB00FBF-3C43-4495-A565-A3CA0465ABBA}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="Resistance"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
-  <hyperlinks>
-    <hyperlink ref="B31" r:id="rId1" display="http://flybase.org/cgi-bin/gbrowse2/dmel/?ref=X%3Bstart%3D20133406%3Bstop%3D20133406" xr:uid="{B8FC0999-7616-49F1-87A3-1B3E3F59521B}"/>
-    <hyperlink ref="B32" r:id="rId2" display="http://flybase.org/cgi-bin/gbrowse2/dmel/?ref=X%3Bstart%3D20133406%3Bstop%3D20133406" xr:uid="{D12D4682-7263-4AE7-87E3-952622B7910D}"/>
-    <hyperlink ref="B33" r:id="rId3" display="http://flybase.org/cgi-bin/gbrowse2/dmel/?ref=2R%3Bstart%3D20102058%3Bstop%3D20102058" xr:uid="{4CBBAB56-1993-4D42-B06B-E2ADADC0A325}"/>
-    <hyperlink ref="B34" r:id="rId4" display="http://flybase.org/cgi-bin/gbrowse2/dmel/?ref=X%3Bstart%3D20032422%3Bstop%3D20032422" xr:uid="{3472204B-D87C-44FF-85AA-19C18FAE29E9}"/>
-    <hyperlink ref="B35" r:id="rId5" display="http://flybase.org/cgi-bin/gbrowse2/dmel/?ref=2R%3Bstart%3D22444306%3Bstop%3D22444306" xr:uid="{3CA6440D-DF0C-4932-9C8B-DB146891372D}"/>
-    <hyperlink ref="B36" r:id="rId6" display="http://flybase.org/cgi-bin/gbrowse2/dmel/?ref=3L%3Bstart%3D1909764%3Bstop%3D1909764" xr:uid="{8AD10B38-7822-4E4A-B260-545000087745}"/>
-    <hyperlink ref="B37" r:id="rId7" display="http://flybase.org/cgi-bin/gbrowse2/dmel/?ref=2R%3Bstart%3D21681039%3Bstop%3D21681039" xr:uid="{6F14B368-4076-44B4-B602-85BB1D4353B6}"/>
-    <hyperlink ref="B38" r:id="rId8" display="http://flybase.org/cgi-bin/gbrowse2/dmel/?ref=X%3Bstart%3D5760226%3Bstop%3D5760226" xr:uid="{9A9B9386-015C-468E-A165-04EC6000DEB0}"/>
-    <hyperlink ref="B39" r:id="rId9" display="http://flybase.org/cgi-bin/gbrowse2/dmel/?ref=3L%3Bstart%3D1108730%3Bstop%3D1108730" xr:uid="{8F216621-19B8-4D14-96C2-D832D0A74CAB}"/>
-    <hyperlink ref="B40" r:id="rId10" display="http://flybase.org/cgi-bin/gbrowse2/dmel/?ref=2L%3Bstart%3D382411%3Bstop%3D382411" xr:uid="{A94C7AF1-F07A-452F-AC6E-3EFD38B6B70A}"/>
-    <hyperlink ref="B41" r:id="rId11" display="http://flybase.org/cgi-bin/gbrowse2/dmel/?ref=X%3Bstart%3D18923524%3Bstop%3D18923524" xr:uid="{1A6D0A06-BDCD-4BD5-A471-383DA24B76C5}"/>
-    <hyperlink ref="B42" r:id="rId12" display="http://flybase.org/cgi-bin/gbrowse2/dmel/?ref=X%3Bstart%3D18923637%3Bstop%3D18923637" xr:uid="{6C09588D-212A-40AE-A14B-7CEB950BAA90}"/>
-    <hyperlink ref="B43" r:id="rId13" display="http://flybase.org/cgi-bin/gbrowse2/dmel/?ref=2R%3Bstart%3D20102018%3Bstop%3D20102018" xr:uid="{B5A2DDC7-104A-4960-89FB-A5053666AD5B}"/>
-    <hyperlink ref="B44" r:id="rId14" display="http://flybase.org/cgi-bin/gbrowse2/dmel/?ref=X%3Bstart%3D20854194%3Bstop%3D20854194" xr:uid="{BB444F80-661D-4676-823B-8DB9B9AD12FE}"/>
-    <hyperlink ref="B45" r:id="rId15" display="http://flybase.org/cgi-bin/gbrowse2/dmel/?ref=2L%3Bstart%3D9926696%3Bstop%3D9926696" xr:uid="{7EFB070E-DA5E-4667-8325-6B9025F93C60}"/>
-    <hyperlink ref="B46" r:id="rId16" display="http://flybase.org/cgi-bin/gbrowse2/dmel/?ref=2R%3Bstart%3D20289946%3Bstop%3D20289946" xr:uid="{A7A6B60A-C061-4A46-ABE8-6445ABD7CDBF}"/>
-    <hyperlink ref="B47" r:id="rId17" display="http://flybase.org/cgi-bin/gbrowse2/dmel/?ref=2R%3Bstart%3D20289993%3Bstop%3D20289993" xr:uid="{78C1DE7D-6D6E-481A-8623-358386BB6FA1}"/>
-    <hyperlink ref="B48" r:id="rId18" display="http://flybase.org/cgi-bin/gbrowse2/dmel/?ref=3R%3Bstart%3D30255259%3Bstop%3D30255259" xr:uid="{4F4924A5-807E-4A11-8F73-0C064B5AD0A0}"/>
-    <hyperlink ref="B49" r:id="rId19" display="http://flybase.org/cgi-bin/gbrowse2/dmel/?ref=3R%3Bstart%3D30255259%3Bstop%3D30255259" xr:uid="{12EB3B9E-6E7F-4388-ACF5-E78CF76FDFCC}"/>
-    <hyperlink ref="B50" r:id="rId20" display="http://flybase.org/cgi-bin/gbrowse2/dmel/?ref=X%3Bstart%3D6206890%3Bstop%3D6206890" xr:uid="{AA01B27A-E82A-4E21-AE1B-0A72D92EBD72}"/>
-    <hyperlink ref="B51" r:id="rId21" display="http://flybase.org/cgi-bin/gbrowse2/dmel/?ref=X%3Bstart%3D20707400%3Bstop%3D20707400" xr:uid="{DACEC6E2-2BB7-4B2F-A7C1-6388E0C3095F}"/>
-    <hyperlink ref="B52" r:id="rId22" display="http://flybase.org/cgi-bin/gbrowse2/dmel/?ref=2L%3Bstart%3D10686264%3Bstop%3D10686264" xr:uid="{D2005733-4CD5-4C2F-AACE-85C73458514E}"/>
-    <hyperlink ref="B53" r:id="rId23" display="http://flybase.org/cgi-bin/gbrowse2/dmel/?ref=2L%3Bstart%3D10686264%3Bstop%3D10686264" xr:uid="{5594F766-E3E0-4832-8107-0E0CF6ACFC5E}"/>
-    <hyperlink ref="B54" r:id="rId24" display="http://flybase.org/cgi-bin/gbrowse2/dmel/?ref=2L%3Bstart%3D383384%3Bstop%3D383384" xr:uid="{C1B2BB6E-4AE3-47CE-ACC9-58E1415CAAE9}"/>
-    <hyperlink ref="B55" r:id="rId25" display="http://flybase.org/cgi-bin/gbrowse2/dmel/?ref=2R%3Bstart%3D18866081%3Bstop%3D18866081" xr:uid="{47E3B26A-43B4-4FF6-A786-08FC2344EE4B}"/>
-    <hyperlink ref="B56" r:id="rId26" display="http://flybase.org/cgi-bin/gbrowse2/dmel/?ref=X%3Bstart%3D9230968%3Bstop%3D9230968" xr:uid="{3D3BEBCB-6749-4D45-9F04-09694F962908}"/>
-    <hyperlink ref="B57" r:id="rId27" display="http://flybase.org/cgi-bin/gbrowse2/dmel/?ref=3L%3Bstart%3D8732726%3Bstop%3D8732726" xr:uid="{8CDBC356-1EE0-41D1-9E54-E12B5AC5B51C}"/>
-    <hyperlink ref="B58" r:id="rId28" display="http://flybase.org/cgi-bin/gbrowse2/dmel/?ref=3L%3Bstart%3D8732726%3Bstop%3D8732726" xr:uid="{7795A3D8-AB31-46CA-8C3C-4F5977163118}"/>
-    <hyperlink ref="B59" r:id="rId29" display="http://flybase.org/cgi-bin/gbrowse2/dmel/?ref=3L%3Bstart%3D15942843%3Bstop%3D15942843" xr:uid="{006705CB-B43D-4861-8FC4-63B48AB33415}"/>
-  </hyperlinks>
+  <autoFilter ref="A1:G59" xr:uid="{6DB00FBF-3C43-4495-A565-A3CA0465ABBA}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Immunity/Tolerance.v.Resistance/Howick_2017/Howick_SNPs.xlsx
+++ b/Immunity/Tolerance.v.Resistance/Howick_2017/Howick_SNPs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://adcsuf-my.sharepoint.com/personal/tconyers_csu_fullerton_edu/Documents/Documents/GitHub/Thesis_Project/Immunity/Tolerance.v.Resistance/Howick_2017/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="13_ncr:1_{47B885E6-3241-4A1F-A9E3-646E238A6E14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{871AE8A1-847E-47EB-87E1-48C5B864ED3A}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="13_ncr:1_{47B885E6-3241-4A1F-A9E3-646E238A6E14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E2A8E22B-C1E2-4D79-927D-7857B017BB40}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -354,9 +354,6 @@
     </r>
   </si>
   <si>
-    <t>3L:8,771,126</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="9"/>
@@ -377,12 +374,6 @@
     </r>
   </si>
   <si>
-    <t>2L:8,895,939</t>
-  </si>
-  <si>
-    <t>2L:1,766,283</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="9"/>
@@ -393,9 +384,6 @@
     </r>
   </si>
   <si>
-    <t>3R:7,586,053</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="9"/>
@@ -406,9 +394,6 @@
     </r>
   </si>
   <si>
-    <t>2L:20,997,569</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="9"/>
@@ -419,9 +404,6 @@
     </r>
   </si>
   <si>
-    <t>2L:15,772,825</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="9"/>
@@ -432,9 +414,6 @@
     </r>
   </si>
   <si>
-    <t>2L:8,896,128</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="9"/>
@@ -445,9 +424,6 @@
     </r>
   </si>
   <si>
-    <t>2L:1,766,281</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="9"/>
@@ -458,9 +434,6 @@
     </r>
   </si>
   <si>
-    <t>2R:5,126,594</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="9"/>
@@ -471,9 +444,6 @@
     </r>
   </si>
   <si>
-    <t>2R:14,681,641</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="9"/>
@@ -484,9 +454,6 @@
     </r>
   </si>
   <si>
-    <t>2L:16,578,056</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="9"/>
@@ -497,9 +464,6 @@
     </r>
   </si>
   <si>
-    <t>2R:15,517,660</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="9"/>
@@ -520,9 +484,6 @@
     </r>
   </si>
   <si>
-    <t>3L:18,601,807</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="9"/>
@@ -533,9 +494,6 @@
     </r>
   </si>
   <si>
-    <t>2R:14,648,549</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="9"/>
@@ -546,9 +504,6 @@
     </r>
   </si>
   <si>
-    <t>2R:17,988,140</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="9"/>
@@ -559,9 +514,6 @@
     </r>
   </si>
   <si>
-    <t>3L:5,645,490</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="9"/>
@@ -572,9 +524,6 @@
     </r>
   </si>
   <si>
-    <t>2L:17,229,914</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="9"/>
@@ -585,9 +534,6 @@
     </r>
   </si>
   <si>
-    <t>3R:21,510,537</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="9"/>
@@ -608,12 +554,6 @@
     </r>
   </si>
   <si>
-    <t>2R:21,323,134</t>
-  </si>
-  <si>
-    <t>2L:16,628,423</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="9"/>
@@ -624,9 +564,6 @@
     </r>
   </si>
   <si>
-    <t>2R:5,332,144</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="9"/>
@@ -637,9 +574,6 @@
     </r>
   </si>
   <si>
-    <t>2R:17,840,479</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="9"/>
@@ -650,9 +584,6 @@
     </r>
   </si>
   <si>
-    <t>2L:533,659</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="9"/>
@@ -663,9 +594,6 @@
     </r>
   </si>
   <si>
-    <t>2R:5,128,902</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="9"/>
@@ -676,9 +604,6 @@
     </r>
   </si>
   <si>
-    <t>X:12,140,511</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="9"/>
@@ -689,9 +614,6 @@
     </r>
   </si>
   <si>
-    <t>2R:5,128,972</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="9"/>
@@ -700,12 +622,6 @@
       </rPr>
       <t>psq</t>
     </r>
-  </si>
-  <si>
-    <t>2R:10,563,254</t>
-  </si>
-  <si>
-    <t>X:21,581,423</t>
   </si>
   <si>
     <t>Tolerance</t>
@@ -795,79 +711,163 @@
     </r>
   </si>
   <si>
-    <t>X:20,133,406</t>
-  </si>
-  <si>
-    <t>2R:20,102,058</t>
-  </si>
-  <si>
-    <t>X:20,032,422</t>
-  </si>
-  <si>
-    <t>2R:22,444,306</t>
-  </si>
-  <si>
-    <t>3L:1,909,764</t>
-  </si>
-  <si>
-    <t>2R:21,681,039</t>
-  </si>
-  <si>
-    <t>X:5,760,226</t>
-  </si>
-  <si>
-    <t>3L:1,108,730</t>
-  </si>
-  <si>
-    <t>2L:382,411</t>
-  </si>
-  <si>
-    <t>X:18,923,524</t>
-  </si>
-  <si>
-    <t>X:18,923,637</t>
-  </si>
-  <si>
-    <t>2R:20,102,018</t>
-  </si>
-  <si>
-    <t>X:20,854,194</t>
-  </si>
-  <si>
-    <t>2L:9,926,696</t>
-  </si>
-  <si>
-    <t>2R:20,289,946</t>
-  </si>
-  <si>
-    <t>2R:20,289,993</t>
-  </si>
-  <si>
-    <t>3R:30,255,259</t>
-  </si>
-  <si>
-    <t>X:6,206,890</t>
-  </si>
-  <si>
-    <t>X:20,707,400</t>
-  </si>
-  <si>
-    <t>2L:10,686,264</t>
-  </si>
-  <si>
-    <t>2L:383,384</t>
-  </si>
-  <si>
-    <t>2R:18,866,081</t>
-  </si>
-  <si>
-    <t>X:9,230,968</t>
-  </si>
-  <si>
-    <t>3L:8,732,726</t>
-  </si>
-  <si>
-    <t>3L:15,942,843</t>
+    <t>X:21581423</t>
+  </si>
+  <si>
+    <t>2R:10563254</t>
+  </si>
+  <si>
+    <t>2R:5128972</t>
+  </si>
+  <si>
+    <t>X:12140511</t>
+  </si>
+  <si>
+    <t>2R:5128902</t>
+  </si>
+  <si>
+    <t>2L:533659</t>
+  </si>
+  <si>
+    <t>2R:17840479</t>
+  </si>
+  <si>
+    <t>2R:5332144</t>
+  </si>
+  <si>
+    <t>2L:16628423</t>
+  </si>
+  <si>
+    <t>2R:21323134</t>
+  </si>
+  <si>
+    <t>3R:21510537</t>
+  </si>
+  <si>
+    <t>2L:17229914</t>
+  </si>
+  <si>
+    <t>3L:5645490</t>
+  </si>
+  <si>
+    <t>2R:17988140</t>
+  </si>
+  <si>
+    <t>2R:14648549</t>
+  </si>
+  <si>
+    <t>3L:18601807</t>
+  </si>
+  <si>
+    <t>2R:15517660</t>
+  </si>
+  <si>
+    <t>2L:16578056</t>
+  </si>
+  <si>
+    <t>2R:14681641</t>
+  </si>
+  <si>
+    <t>2R:5126594</t>
+  </si>
+  <si>
+    <t>2L:1766281</t>
+  </si>
+  <si>
+    <t>2L:8896128</t>
+  </si>
+  <si>
+    <t>2L:15772825</t>
+  </si>
+  <si>
+    <t>2L:20997569</t>
+  </si>
+  <si>
+    <t>3R:7586053</t>
+  </si>
+  <si>
+    <t>2L:1766283</t>
+  </si>
+  <si>
+    <t>2L:8895939</t>
+  </si>
+  <si>
+    <t>3L:8771126</t>
+  </si>
+  <si>
+    <t>X:20133406</t>
+  </si>
+  <si>
+    <t>2R:20102058</t>
+  </si>
+  <si>
+    <t>X:20032422</t>
+  </si>
+  <si>
+    <t>2R:22444306</t>
+  </si>
+  <si>
+    <t>3L:1909764</t>
+  </si>
+  <si>
+    <t>2R:21681039</t>
+  </si>
+  <si>
+    <t>X:5760226</t>
+  </si>
+  <si>
+    <t>3L:1108730</t>
+  </si>
+  <si>
+    <t>2L:382411</t>
+  </si>
+  <si>
+    <t>X:18923524</t>
+  </si>
+  <si>
+    <t>X:18923637</t>
+  </si>
+  <si>
+    <t>2R:20102018</t>
+  </si>
+  <si>
+    <t>X:20854194</t>
+  </si>
+  <si>
+    <t>2L:9926696</t>
+  </si>
+  <si>
+    <t>2R:20289946</t>
+  </si>
+  <si>
+    <t>2R:20289993</t>
+  </si>
+  <si>
+    <t>3R:30255259</t>
+  </si>
+  <si>
+    <t>X:6206890</t>
+  </si>
+  <si>
+    <t>X:20707400</t>
+  </si>
+  <si>
+    <t>2L:10686264</t>
+  </si>
+  <si>
+    <t>2L:383384</t>
+  </si>
+  <si>
+    <t>2R:18866081</t>
+  </si>
+  <si>
+    <t>X:9230968</t>
+  </si>
+  <si>
+    <t>3L:8732726</t>
+  </si>
+  <si>
+    <t>3L:15942843</t>
   </si>
 </sst>
 </file>
@@ -1439,33 +1439,33 @@
   <sheetData>
     <row r="1" spans="1:7" ht="24" x14ac:dyDescent="0.25">
       <c r="A1" s="44" t="s">
-        <v>88</v>
+        <v>60</v>
       </c>
       <c r="B1" s="44" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="44" t="s">
-        <v>89</v>
+        <v>61</v>
       </c>
       <c r="D1" s="45" t="s">
-        <v>90</v>
+        <v>62</v>
       </c>
       <c r="E1" s="44" t="s">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="F1" s="45" t="s">
-        <v>92</v>
+        <v>64</v>
       </c>
       <c r="G1" s="43" t="s">
-        <v>93</v>
+        <v>65</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="42" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
       <c r="B2" s="42" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="C2" s="42" t="s">
         <v>4</v>
@@ -1485,13 +1485,13 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="42" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
       <c r="B3" s="35" t="s">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="C3" s="35" t="s">
-        <v>83</v>
+        <v>57</v>
       </c>
       <c r="D3" s="35" t="s">
         <v>9</v>
@@ -1508,16 +1508,16 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="42" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
       <c r="B4" s="39" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="C4" s="39" t="s">
-        <v>77</v>
+        <v>54</v>
       </c>
       <c r="D4" s="39" t="s">
-        <v>81</v>
+        <v>56</v>
       </c>
       <c r="E4" s="38">
         <v>1.39E-6</v>
@@ -1531,13 +1531,13 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="42" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
       <c r="B5" s="35" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="C5" s="35" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
       <c r="D5" s="35" t="s">
         <v>9</v>
@@ -1554,13 +1554,13 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="42" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
       <c r="B6" s="39" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="C6" s="39" t="s">
-        <v>77</v>
+        <v>54</v>
       </c>
       <c r="D6" s="39" t="s">
         <v>9</v>
@@ -1577,13 +1577,13 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="42" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
       <c r="B7" s="35" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="C7" s="35" t="s">
-        <v>75</v>
+        <v>53</v>
       </c>
       <c r="D7" s="35" t="s">
         <v>9</v>
@@ -1600,13 +1600,13 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="42" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
       <c r="B8" s="39" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C8" s="39" t="s">
-        <v>73</v>
+        <v>52</v>
       </c>
       <c r="D8" s="39" t="s">
         <v>11</v>
@@ -1623,13 +1623,13 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="42" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
       <c r="B9" s="35" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C9" s="35" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="D9" s="35" t="s">
         <v>19</v>
@@ -1646,13 +1646,13 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="42" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
       <c r="B10" s="39" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C10" s="39" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="D10" s="39" t="s">
         <v>9</v>
@@ -1669,16 +1669,16 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="42" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
       <c r="B11" s="35" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C11" s="35" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="D11" s="35" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="E11" s="34">
         <v>4.8799999999999999E-6</v>
@@ -1692,13 +1692,13 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="42" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
       <c r="B12" s="39" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="C12" s="39" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="D12" s="39" t="s">
         <v>9</v>
@@ -1715,13 +1715,13 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="42" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
       <c r="B13" s="35" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="C13" s="35" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="D13" s="35" t="s">
         <v>9</v>
@@ -1738,13 +1738,13 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="42" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
       <c r="B14" s="39" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="C14" s="39" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="D14" s="39" t="s">
         <v>9</v>
@@ -1761,13 +1761,13 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="42" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
       <c r="B15" s="35" t="s">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="C15" s="35" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="D15" s="35" t="s">
         <v>9</v>
@@ -1784,13 +1784,13 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="42" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
       <c r="B16" s="39" t="s">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="C16" s="39" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="D16" s="39" t="s">
         <v>19</v>
@@ -1807,16 +1807,16 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="42" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
       <c r="B17" s="35" t="s">
-        <v>56</v>
+        <v>81</v>
       </c>
       <c r="C17" s="35" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="D17" s="35" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="E17" s="34">
         <v>5.9100000000000002E-6</v>
@@ -1830,13 +1830,13 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="42" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
       <c r="B18" s="39" t="s">
-        <v>53</v>
+        <v>82</v>
       </c>
       <c r="C18" s="39" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="D18" s="39" t="s">
         <v>13</v>
@@ -1853,13 +1853,13 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="42" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
       <c r="B19" s="35" t="s">
-        <v>51</v>
+        <v>83</v>
       </c>
       <c r="C19" s="35" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="D19" s="35" t="s">
         <v>9</v>
@@ -1876,13 +1876,13 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="42" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
       <c r="B20" s="39" t="s">
-        <v>49</v>
+        <v>84</v>
       </c>
       <c r="C20" s="39" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="D20" s="39" t="s">
         <v>9</v>
@@ -1899,13 +1899,13 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="42" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
       <c r="B21" s="35" t="s">
-        <v>47</v>
+        <v>85</v>
       </c>
       <c r="C21" s="35" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="D21" s="35" t="s">
         <v>9</v>
@@ -1922,10 +1922,10 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="42" t="s">
+        <v>58</v>
+      </c>
+      <c r="B22" s="39" t="s">
         <v>86</v>
-      </c>
-      <c r="B22" s="39" t="s">
-        <v>45</v>
       </c>
       <c r="C22" s="39" t="s">
         <v>4</v>
@@ -1945,13 +1945,13 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="42" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
       <c r="B23" s="35" t="s">
-        <v>43</v>
+        <v>87</v>
       </c>
       <c r="C23" s="35" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="D23" s="35" t="s">
         <v>19</v>
@@ -1968,13 +1968,13 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="42" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
       <c r="B24" s="39" t="s">
-        <v>43</v>
+        <v>87</v>
       </c>
       <c r="C24" s="39" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="D24" s="39" t="s">
         <v>2</v>
@@ -1991,13 +1991,13 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="42" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
       <c r="B25" s="35" t="s">
-        <v>41</v>
+        <v>88</v>
       </c>
       <c r="C25" s="35" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="D25" s="35" t="s">
         <v>9</v>
@@ -2014,13 +2014,13 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="42" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
       <c r="B26" s="39" t="s">
-        <v>39</v>
+        <v>89</v>
       </c>
       <c r="C26" s="39" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D26" s="39" t="s">
         <v>9</v>
@@ -2037,13 +2037,13 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="42" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
       <c r="B27" s="35" t="s">
-        <v>37</v>
+        <v>90</v>
       </c>
       <c r="C27" s="35" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D27" s="35" t="s">
         <v>9</v>
@@ -2060,10 +2060,10 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="42" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
       <c r="B28" s="39" t="s">
-        <v>35</v>
+        <v>91</v>
       </c>
       <c r="C28" s="39" t="s">
         <v>4</v>
@@ -2083,16 +2083,16 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="42" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
       <c r="B29" s="36" t="s">
-        <v>34</v>
+        <v>92</v>
       </c>
       <c r="C29" s="35" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D29" s="35" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E29" s="34">
         <v>9.4399999999999994E-6</v>
@@ -2106,10 +2106,10 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="42" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
       <c r="B30" s="32" t="s">
-        <v>31</v>
+        <v>93</v>
       </c>
       <c r="C30" s="32" t="s">
         <v>30</v>
@@ -2129,7 +2129,7 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="42" t="s">
-        <v>87</v>
+        <v>59</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>94</v>
@@ -2152,7 +2152,7 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="42" t="s">
-        <v>87</v>
+        <v>59</v>
       </c>
       <c r="B32" s="6" t="s">
         <v>94</v>
@@ -2175,7 +2175,7 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="42" t="s">
-        <v>87</v>
+        <v>59</v>
       </c>
       <c r="B33" s="11" t="s">
         <v>95</v>
@@ -2198,7 +2198,7 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="42" t="s">
-        <v>87</v>
+        <v>59</v>
       </c>
       <c r="B34" s="6" t="s">
         <v>96</v>
@@ -2221,7 +2221,7 @@
     </row>
     <row r="35" spans="1:7" ht="22.8" x14ac:dyDescent="0.25">
       <c r="A35" s="42" t="s">
-        <v>87</v>
+        <v>59</v>
       </c>
       <c r="B35" s="11" t="s">
         <v>97</v>
@@ -2244,7 +2244,7 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="42" t="s">
-        <v>87</v>
+        <v>59</v>
       </c>
       <c r="B36" s="6" t="s">
         <v>98</v>
@@ -2267,7 +2267,7 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="42" t="s">
-        <v>87</v>
+        <v>59</v>
       </c>
       <c r="B37" s="11" t="s">
         <v>99</v>
@@ -2290,7 +2290,7 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="42" t="s">
-        <v>87</v>
+        <v>59</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>100</v>
@@ -2313,7 +2313,7 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="42" t="s">
-        <v>87</v>
+        <v>59</v>
       </c>
       <c r="B39" s="20" t="s">
         <v>101</v>
@@ -2336,7 +2336,7 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="42" t="s">
-        <v>87</v>
+        <v>59</v>
       </c>
       <c r="B40" s="6" t="s">
         <v>102</v>
@@ -2359,7 +2359,7 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="42" t="s">
-        <v>87</v>
+        <v>59</v>
       </c>
       <c r="B41" s="20" t="s">
         <v>103</v>
@@ -2382,7 +2382,7 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="42" t="s">
-        <v>87</v>
+        <v>59</v>
       </c>
       <c r="B42" s="6" t="s">
         <v>104</v>
@@ -2405,7 +2405,7 @@
     </row>
     <row r="43" spans="1:7" ht="22.8" x14ac:dyDescent="0.25">
       <c r="A43" s="42" t="s">
-        <v>87</v>
+        <v>59</v>
       </c>
       <c r="B43" s="11" t="s">
         <v>105</v>
@@ -2428,7 +2428,7 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="42" t="s">
-        <v>87</v>
+        <v>59</v>
       </c>
       <c r="B44" s="6" t="s">
         <v>106</v>
@@ -2451,7 +2451,7 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="42" t="s">
-        <v>87</v>
+        <v>59</v>
       </c>
       <c r="B45" s="11" t="s">
         <v>107</v>
@@ -2474,7 +2474,7 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="42" t="s">
-        <v>87</v>
+        <v>59</v>
       </c>
       <c r="B46" s="6" t="s">
         <v>108</v>
@@ -2497,7 +2497,7 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="42" t="s">
-        <v>87</v>
+        <v>59</v>
       </c>
       <c r="B47" s="11" t="s">
         <v>109</v>
@@ -2520,7 +2520,7 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="42" t="s">
-        <v>87</v>
+        <v>59</v>
       </c>
       <c r="B48" s="6" t="s">
         <v>110</v>
@@ -2543,7 +2543,7 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="42" t="s">
-        <v>87</v>
+        <v>59</v>
       </c>
       <c r="B49" s="11" t="s">
         <v>110</v>
@@ -2566,7 +2566,7 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="42" t="s">
-        <v>87</v>
+        <v>59</v>
       </c>
       <c r="B50" s="6" t="s">
         <v>111</v>
@@ -2589,7 +2589,7 @@
     </row>
     <row r="51" spans="1:7" ht="22.8" x14ac:dyDescent="0.25">
       <c r="A51" s="42" t="s">
-        <v>87</v>
+        <v>59</v>
       </c>
       <c r="B51" s="11" t="s">
         <v>112</v>
@@ -2612,7 +2612,7 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="42" t="s">
-        <v>87</v>
+        <v>59</v>
       </c>
       <c r="B52" s="6" t="s">
         <v>113</v>
@@ -2635,7 +2635,7 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="42" t="s">
-        <v>87</v>
+        <v>59</v>
       </c>
       <c r="B53" s="11" t="s">
         <v>113</v>
@@ -2658,7 +2658,7 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="42" t="s">
-        <v>87</v>
+        <v>59</v>
       </c>
       <c r="B54" s="6" t="s">
         <v>114</v>
@@ -2681,7 +2681,7 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="42" t="s">
-        <v>87</v>
+        <v>59</v>
       </c>
       <c r="B55" s="11" t="s">
         <v>115</v>
@@ -2704,7 +2704,7 @@
     </row>
     <row r="56" spans="1:7" ht="22.8" x14ac:dyDescent="0.25">
       <c r="A56" s="42" t="s">
-        <v>87</v>
+        <v>59</v>
       </c>
       <c r="B56" s="6" t="s">
         <v>116</v>
@@ -2727,7 +2727,7 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="42" t="s">
-        <v>87</v>
+        <v>59</v>
       </c>
       <c r="B57" s="11" t="s">
         <v>117</v>
@@ -2750,7 +2750,7 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="42" t="s">
-        <v>87</v>
+        <v>59</v>
       </c>
       <c r="B58" s="6" t="s">
         <v>117</v>
@@ -2773,7 +2773,7 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="42" t="s">
-        <v>87</v>
+        <v>59</v>
       </c>
       <c r="B59" s="25" t="s">
         <v>118</v>
